--- a/samples/03_fact_december_corrected.xlsx
+++ b/samples/03_fact_december_corrected.xlsx
@@ -454,29 +454,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Аренда</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>400000</v>
+        <v>124928.53</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Продажи</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Закупки товара</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36761.63</v>
+        <v>344802.47</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -490,29 +490,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Зарплата</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1082034.21</v>
+        <v>106431.87</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Офис</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Зарплата</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72822.78</v>
+        <v>1201488.65</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -522,15 +522,15 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45998</v>
+        <v>45996</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37803.53</v>
+        <v>46477.58</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -540,25 +540,25 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45999</v>
+        <v>45997</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Связь и ПО</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42437.13</v>
+        <v>72346.31</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Офис</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46001</v>
+        <v>45998</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>388583.97</v>
+        <v>539934.75</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -576,15 +576,15 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46001</v>
+        <v>45999</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Маркетинг</t>
+          <t>Закупки товара</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39427.38</v>
+        <v>403118.95</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46003</v>
+        <v>46000</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>484778.45</v>
+        <v>488682.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -612,33 +612,33 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46003</v>
+        <v>46000</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>67721.25999999999</v>
+        <v>33801.69</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Склад</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46004</v>
+        <v>46001</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Закупки товара</t>
+          <t>Аренда</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>222856.21</v>
+        <v>439000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -656,17 +656,17 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>344330.48</v>
+        <v>391399.99</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Продажи</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>370773.31</v>
+        <v>694253.51</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -684,33 +684,33 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Зарплата</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1017965.79</v>
+        <v>121047.12</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Продажи</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46009</v>
+        <v>46005</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>112242.36</v>
+        <v>48378.79</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -720,15 +720,15 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Связь и ПО</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>73782.78999999999</v>
+        <v>92062.71000000001</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -746,25 +746,25 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35694.96</v>
+        <v>43438.62</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Склад</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46012</v>
+        <v>46008</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Закупки товара</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>490646.73</v>
+        <v>59124.52</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -782,25 +782,25 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>478769.12</v>
+        <v>487251.47</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Продажи</t>
+          <t>Склад</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46013</v>
+        <v>46012</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Связь и ПО</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>115305.4</v>
+        <v>89653.69</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -810,15 +810,15 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46014</v>
+        <v>46013</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Закупки товара</t>
+          <t>Зарплата</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>420586.84</v>
+        <v>839511.35</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -828,51 +828,51 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46016</v>
+        <v>46014</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Закупки товара</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>398674.89</v>
+        <v>55871.02</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Склад</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46016</v>
+        <v>46015</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Закупки товара</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>42285.66</v>
+        <v>395135.65</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Продажи</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46018</v>
+        <v>46017</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Связь и ПО</t>
+          <t>Логистика</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>86217.21000000001</v>
+        <v>94927.67</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -882,25 +882,25 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46022</v>
+        <v>46019</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Логистика</t>
+          <t>Закупки товара</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>67185.41</v>
+        <v>442420.91</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Офис</t>
+          <t>Продажи</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46022</v>
+        <v>46019</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -908,11 +908,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>30312.5</v>
+        <v>58509.88</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Склад</t>
+          <t>Офис</t>
         </is>
       </c>
     </row>
